--- a/artfynd/Juvtábákte utvidgning S artfynd.xlsx
+++ b/artfynd/Juvtábákte utvidgning S artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047484</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047482</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047478</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047479</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6232328</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135268088</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047481</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4048553</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4385026</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5927942</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1800,6 +1855,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5995463</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1902,6 +1962,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6196197</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2004,6 +2069,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6221647</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2106,6 +2176,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6222870</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2212,6 +2287,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6232315</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2332,6 +2412,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68739041</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2434,6 +2519,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72337580</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2531,6 +2621,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047480</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2628,6 +2723,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047703</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2725,6 +2825,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047700</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2822,6 +2927,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047708</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2919,6 +3029,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047712</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3016,8 +3131,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047705</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Juvtábákte utvidgning S artfynd.xlsx
+++ b/artfynd/Juvtábákte utvidgning S artfynd.xlsx
@@ -1202,7 +1202,7 @@
         <v>135268088</v>
       </c>
       <c r="B7" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/Juvtábákte utvidgning S artfynd.xlsx
+++ b/artfynd/Juvtábákte utvidgning S artfynd.xlsx
@@ -1202,7 +1202,7 @@
         <v>135268088</v>
       </c>
       <c r="B7" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/Juvtábákte utvidgning S artfynd.xlsx
+++ b/artfynd/Juvtábákte utvidgning S artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135268088</v>
+        <v>110047481</v>
       </c>
       <c r="B7" t="n">
-        <v>79461</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,34 +1210,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>260591</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Basseviken, Basseviken, Pi lm</t>
+          <t>Akkelis utvidgning-Silvervägen, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611391</v>
+        <v>612230</v>
       </c>
       <c r="R7" t="n">
-        <v>7334520</v>
+        <v>7333939</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,89 +1280,69 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135268088</t>
+          <t>https://artportalen.se/Sighting/110047481</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110047481</v>
+        <v>4048553</v>
       </c>
       <c r="B8" t="n">
-        <v>93197</v>
+        <v>106229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Akkelis utvidgning-Silvervägen, Pi lm</t>
+          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612230</v>
+        <v>612320</v>
       </c>
       <c r="R8" t="n">
-        <v>7333939</v>
+        <v>7333807</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,12 +1366,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2009-07-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2009-07-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,31 +1382,40 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>vägslänt</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lennart Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Lennart Persson, Arne Lysell, Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110047481</t>
+          <t>https://artportalen.se/Sighting/4048553</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4048553</v>
+        <v>4385026</v>
       </c>
       <c r="B9" t="n">
-        <v>106229</v>
+        <v>99140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,37 +1423,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
+          <t>Östansjö, 1900 m NV i myr S landsvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612320</v>
+        <v>612281</v>
       </c>
       <c r="R9" t="n">
-        <v>7333807</v>
+        <v>7333726</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,7 +1496,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>vägslänt</t>
+          <t>myr</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1518,7 +1507,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lennart Persson, Arne Lysell, Britta Lidberg</t>
+          <t>Lennart Persson, Britta Lidberg, Arne Lysell</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1528,16 +1517,16 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4048553</t>
+          <t>https://artportalen.se/Sighting/4385026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4385026</v>
+        <v>5927942</v>
       </c>
       <c r="B10" t="n">
-        <v>99140</v>
+        <v>99036</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,37 +1534,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östansjö, 1900 m NV i myr S landsvägen, Pi lm</t>
+          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>612281</v>
+        <v>612320</v>
       </c>
       <c r="R10" t="n">
-        <v>7333726</v>
+        <v>7333807</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,7 +1607,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>myr</t>
+          <t>vägslänt</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1629,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lennart Persson, Britta Lidberg, Arne Lysell</t>
+          <t>Lennart Persson, Arne Lysell, Britta Lidberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1639,16 +1628,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4385026</t>
+          <t>https://artportalen.se/Sighting/5927942</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5927942</v>
+        <v>5995463</v>
       </c>
       <c r="B11" t="n">
-        <v>99036</v>
+        <v>99121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,37 +1645,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223591</v>
+        <v>223614</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vanlig brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
+          <t>Judabakte mot SV vid Silvervägen, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>612320</v>
+        <v>612031</v>
       </c>
       <c r="R11" t="n">
-        <v>7333807</v>
+        <v>7333998</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1710,12 +1695,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,12 +1720,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lennart Persson</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lennart Persson, Arne Lysell, Britta Lidberg</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1750,16 +1735,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5927942</t>
+          <t>https://artportalen.se/Sighting/5995463</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5995463</v>
+        <v>6196197</v>
       </c>
       <c r="B12" t="n">
-        <v>99121</v>
+        <v>97990</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,33 +1752,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223614</v>
+        <v>224358</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
+          <t>Lycopodium complanatum subsp. complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Judabakte mot SV vid Silvervägen, Pi lm</t>
+          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>612031</v>
+        <v>612320</v>
       </c>
       <c r="R12" t="n">
-        <v>7333998</v>
+        <v>7333807</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1817,12 +1802,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2009-07-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2009-07-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,12 +1827,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Lennart Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+          <t>Lennart Persson, Britta Lidberg, Arne Lysell</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1857,16 +1842,16 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5995463</t>
+          <t>https://artportalen.se/Sighting/6196197</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6196197</v>
+        <v>6221647</v>
       </c>
       <c r="B13" t="n">
-        <v>97990</v>
+        <v>97985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,16 +1859,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224358</v>
+        <v>224363</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1954,7 +1939,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lennart Persson, Britta Lidberg, Arne Lysell</t>
+          <t>Lennart Persson, Arne Lysell, Britta Lidberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1964,13 +1949,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6196197</t>
+          <t>https://artportalen.se/Sighting/6221647</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6221647</v>
+        <v>6222870</v>
       </c>
       <c r="B14" t="n">
         <v>97985</v>
@@ -1997,17 +1982,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
+          <t>Judabakte mot SV vid Silvervägen, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>612320</v>
+        <v>612095</v>
       </c>
       <c r="R14" t="n">
-        <v>7333807</v>
+        <v>7333930</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2031,12 +2016,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,12 +2041,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lennart Persson</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lennart Persson, Arne Lysell, Britta Lidberg</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2071,16 +2056,16 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6221647</t>
+          <t>https://artportalen.se/Sighting/6222870</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6222870</v>
+        <v>6232315</v>
       </c>
       <c r="B15" t="n">
-        <v>97985</v>
+        <v>97988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2088,33 +2073,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224363</v>
+        <v>224365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Riplummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Lycopodium clavatum subsp. monostachyon</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Grev. &amp; Hook.) Selander</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Judabakte mot SV vid Silvervägen, Pi lm</t>
+          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>612095</v>
+        <v>612320</v>
       </c>
       <c r="R15" t="n">
-        <v>7333930</v>
+        <v>7333807</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2138,12 +2127,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2009-07-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2009-07-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,12 +2152,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Lennart Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+          <t>Lennart Persson, Britta Lidberg, Arne Lysell</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2178,54 +2167,58 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6222870</t>
+          <t>https://artportalen.se/Sighting/6232315</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6232315</v>
+        <v>68739041</v>
       </c>
       <c r="B16" t="n">
-        <v>97988</v>
+        <v>106537</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>224365</v>
+        <v>1889</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Riplummer</t>
+          <t>Stickelfrö</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. monostachyon</t>
+          <t>Lappula deflexa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Grev. &amp; Hook.) Selander</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Wahlenb.) Garcke</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
+          <t>Judapakte SO, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>612320</v>
+        <v>612966</v>
       </c>
       <c r="R16" t="n">
-        <v>7333807</v>
+        <v>7333559</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2249,12 +2242,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,18 +2261,28 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>vägslänt</t>
+          <t>under bergbrant</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Umeå-Herbarium UME</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>17-228</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lennart Persson</t>
+          <t>Mats G Nettelbladt</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lennart Persson, Britta Lidberg, Arne Lysell</t>
+          <t>Mats G Nettelbladt, Maj-Lis Granström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2289,58 +2292,54 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6232315</t>
+          <t>https://artportalen.se/Sighting/68739041</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>68739041</v>
+        <v>72337580</v>
       </c>
       <c r="B17" t="n">
-        <v>106537</v>
+        <v>96445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1889</v>
+        <v>2665</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stickelfrö</t>
+          <t>Nordlig fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lappula deflexa</t>
+          <t>Neckera oligocarpa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Wahlenb.) Garcke</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Bruch</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Judapakte SO, Pi lm</t>
+          <t>Mt. Juvtábakte (N of Östansjö, NW of Arjeplog), 445 masl (NHWP488), Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>612966</v>
+        <v>613011</v>
       </c>
       <c r="R17" t="n">
-        <v>7333559</v>
+        <v>7333581</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2364,12 +2363,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
+          <t>2017-08-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
+          <t>2017-08-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2383,85 +2382,71 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>under bergbrant</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>Umeå-Herbarium UME</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>17-228</t>
+          <t>Rock face on steep S.-facing slope in open birch/conifer woodland</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt, Maj-Lis Granström</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Niklas Lönnell, Nick Hodgetts</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68739041</t>
+          <t>https://artportalen.se/Sighting/72337580</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>72337580</v>
+        <v>110047480</v>
       </c>
       <c r="B18" t="n">
-        <v>96445</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2665</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordlig fjädermossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neckera oligocarpa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bruch</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mt. Juvtábakte (N of Östansjö, NW of Arjeplog), 445 masl (NHWP488), Pi lm</t>
+          <t>Akkelis utvidgning-Silvervägen, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613011</v>
+        <v>612979</v>
       </c>
       <c r="R18" t="n">
-        <v>7333581</v>
+        <v>7333708</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2485,12 +2470,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2017-08-23</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2017-08-23</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2501,36 +2486,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Rock face on steep S.-facing slope in open birch/conifer woodland</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Niklas Lönnell, Nick Hodgetts</t>
+          <t>Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72337580</t>
+          <t>https://artportalen.se/Sighting/110047480</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110047480</v>
+        <v>110047703</v>
       </c>
       <c r="B19" t="n">
-        <v>93197</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2562,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>612979</v>
+        <v>614574</v>
       </c>
       <c r="R19" t="n">
-        <v>7333708</v>
+        <v>7334375</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,12 +2572,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2623,16 +2603,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110047480</t>
+          <t>https://artportalen.se/Sighting/110047703</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110047703</v>
+        <v>110047700</v>
       </c>
       <c r="B20" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2640,21 +2620,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2664,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614574</v>
+        <v>614449</v>
       </c>
       <c r="R20" t="n">
-        <v>7334375</v>
+        <v>7334498</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2725,13 +2705,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110047703</t>
+          <t>https://artportalen.se/Sighting/110047700</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110047700</v>
+        <v>110047708</v>
       </c>
       <c r="B21" t="n">
         <v>57953</v>
@@ -2766,10 +2746,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614449</v>
+        <v>614534</v>
       </c>
       <c r="R21" t="n">
-        <v>7334498</v>
+        <v>7334351</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,16 +2807,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110047700</t>
+          <t>https://artportalen.se/Sighting/110047708</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110047708</v>
+        <v>110047712</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>58057</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,16 +2824,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2868,10 +2848,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614534</v>
+        <v>614288</v>
       </c>
       <c r="R22" t="n">
-        <v>7334351</v>
+        <v>7334665</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2929,16 +2909,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110047708</t>
+          <t>https://artportalen.se/Sighting/110047712</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110047712</v>
+        <v>110047705</v>
       </c>
       <c r="B23" t="n">
-        <v>58057</v>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2946,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2970,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614288</v>
+        <v>614619</v>
       </c>
       <c r="R23" t="n">
-        <v>7334665</v>
+        <v>7334406</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,108 +3010,6 @@
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/110047712</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>110047705</v>
-      </c>
-      <c r="B24" t="n">
-        <v>91909</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Akkelis utvidgning-Silvervägen, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>614619</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7334406</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Robert Sandberg</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Frédéric Forsmark</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110047705</t>
         </is>
@@ -3161,7 +3039,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Juvtábákte utvidgning S artfynd.xlsx
+++ b/artfynd/Juvtábákte utvidgning S artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110047481</v>
+        <v>135268088</v>
       </c>
       <c r="B7" t="n">
-        <v>93197</v>
+        <v>79464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,34 +1210,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>260591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Akkelis utvidgning-Silvervägen, Pi lm</t>
+          <t>Basseviken, Basseviken, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>612230</v>
+        <v>611391</v>
       </c>
       <c r="R7" t="n">
-        <v>7333939</v>
+        <v>7334520</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,69 +1280,89 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110047481</t>
+          <t>https://artportalen.se/Sighting/135268088</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4048553</v>
+        <v>110047481</v>
       </c>
       <c r="B8" t="n">
-        <v>106229</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
+          <t>Akkelis utvidgning-Silvervägen, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>612320</v>
+        <v>612230</v>
       </c>
       <c r="R8" t="n">
-        <v>7333807</v>
+        <v>7333939</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1366,12 +1386,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,40 +1402,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>vägslänt</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lennart Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lennart Persson, Arne Lysell, Britta Lidberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Pite lappmarks flora (2007-2018)</t>
-        </is>
-      </c>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4048553</t>
+          <t>https://artportalen.se/Sighting/110047481</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4385026</v>
+        <v>4048553</v>
       </c>
       <c r="B9" t="n">
-        <v>99140</v>
+        <v>106229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,37 +1434,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östansjö, 1900 m NV i myr S landsvägen, Pi lm</t>
+          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>612281</v>
+        <v>612320</v>
       </c>
       <c r="R9" t="n">
-        <v>7333726</v>
+        <v>7333807</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,7 +1507,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>myr</t>
+          <t>vägslänt</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1507,7 +1518,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lennart Persson, Britta Lidberg, Arne Lysell</t>
+          <t>Lennart Persson, Arne Lysell, Britta Lidberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1517,16 +1528,16 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4385026</t>
+          <t>https://artportalen.se/Sighting/4048553</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5927942</v>
+        <v>4385026</v>
       </c>
       <c r="B10" t="n">
-        <v>99036</v>
+        <v>99140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,37 +1545,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
+          <t>Östansjö, 1900 m NV i myr S landsvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>612320</v>
+        <v>612281</v>
       </c>
       <c r="R10" t="n">
-        <v>7333807</v>
+        <v>7333726</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1607,7 +1618,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>vägslänt</t>
+          <t>myr</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1618,7 +1629,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lennart Persson, Arne Lysell, Britta Lidberg</t>
+          <t>Lennart Persson, Britta Lidberg, Arne Lysell</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1628,16 +1639,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5927942</t>
+          <t>https://artportalen.se/Sighting/4385026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5995463</v>
+        <v>5927942</v>
       </c>
       <c r="B11" t="n">
-        <v>99121</v>
+        <v>99036</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,33 +1656,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223614</v>
+        <v>223591</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Judabakte mot SV vid Silvervägen, Pi lm</t>
+          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>612031</v>
+        <v>612320</v>
       </c>
       <c r="R11" t="n">
-        <v>7333998</v>
+        <v>7333807</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,12 +1710,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2009-07-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2009-07-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,12 +1735,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Lennart Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+          <t>Lennart Persson, Arne Lysell, Britta Lidberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,16 +1750,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5995463</t>
+          <t>https://artportalen.se/Sighting/5927942</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6196197</v>
+        <v>5995463</v>
       </c>
       <c r="B12" t="n">
-        <v>97990</v>
+        <v>99121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,33 +1767,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224358</v>
+        <v>223614</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Vanlig brudsporre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
+          <t>Judabakte mot SV vid Silvervägen, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>612320</v>
+        <v>612031</v>
       </c>
       <c r="R12" t="n">
-        <v>7333807</v>
+        <v>7333998</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,12 +1817,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,12 +1842,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lennart Persson</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lennart Persson, Britta Lidberg, Arne Lysell</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1842,16 +1857,16 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6196197</t>
+          <t>https://artportalen.se/Sighting/5995463</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6221647</v>
+        <v>6196197</v>
       </c>
       <c r="B13" t="n">
-        <v>97985</v>
+        <v>97990</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,16 +1874,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224363</v>
+        <v>224358</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Lycopodium complanatum subsp. complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1939,7 +1954,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lennart Persson, Arne Lysell, Britta Lidberg</t>
+          <t>Lennart Persson, Britta Lidberg, Arne Lysell</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1949,13 +1964,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6221647</t>
+          <t>https://artportalen.se/Sighting/6196197</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6222870</v>
+        <v>6221647</v>
       </c>
       <c r="B14" t="n">
         <v>97985</v>
@@ -1982,17 +1997,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Judabakte mot SV vid Silvervägen, Pi lm</t>
+          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>612095</v>
+        <v>612320</v>
       </c>
       <c r="R14" t="n">
-        <v>7333930</v>
+        <v>7333807</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2016,12 +2031,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2009-07-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2011-07-10</t>
+          <t>2009-07-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,12 +2056,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren</t>
+          <t>Lennart Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+          <t>Lennart Persson, Arne Lysell, Britta Lidberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2056,16 +2071,16 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6222870</t>
+          <t>https://artportalen.se/Sighting/6221647</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6232315</v>
+        <v>6222870</v>
       </c>
       <c r="B15" t="n">
-        <v>97988</v>
+        <v>97985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,37 +2088,33 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224365</v>
+        <v>224363</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Riplummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. monostachyon</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Grev. &amp; Hook.) Selander</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
+          <t>Judabakte mot SV vid Silvervägen, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>612320</v>
+        <v>612095</v>
       </c>
       <c r="R15" t="n">
-        <v>7333807</v>
+        <v>7333930</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2127,12 +2138,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2009-07-11</t>
+          <t>2011-07-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2152,12 +2163,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lennart Persson</t>
+          <t>Charlotte Nordgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lennart Persson, Britta Lidberg, Arne Lysell</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2167,58 +2178,54 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6232315</t>
+          <t>https://artportalen.se/Sighting/6222870</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>68739041</v>
+        <v>6232315</v>
       </c>
       <c r="B16" t="n">
-        <v>106537</v>
+        <v>97988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1889</v>
+        <v>224365</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stickelfrö</t>
+          <t>Riplummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lappula deflexa</t>
+          <t>Lycopodium clavatum subsp. monostachyon</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Wahlenb.) Garcke</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Grev. &amp; Hook.) Selander</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Judapakte SO, Pi lm</t>
+          <t>Östansjö, 1960 m NV vid landsvägen, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>612966</v>
+        <v>612320</v>
       </c>
       <c r="R16" t="n">
-        <v>7333559</v>
+        <v>7333807</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2242,12 +2249,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
+          <t>2009-07-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
+          <t>2009-07-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2261,28 +2268,18 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>under bergbrant</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>Umeå-Herbarium UME</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>17-228</t>
+          <t>vägslänt</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt</t>
+          <t>Lennart Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt, Maj-Lis Granström</t>
+          <t>Lennart Persson, Britta Lidberg, Arne Lysell</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2292,54 +2289,58 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68739041</t>
+          <t>https://artportalen.se/Sighting/6232315</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>72337580</v>
+        <v>68739041</v>
       </c>
       <c r="B17" t="n">
-        <v>96445</v>
+        <v>106537</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2665</v>
+        <v>1889</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordlig fjädermossa</t>
+          <t>Stickelfrö</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neckera oligocarpa</t>
+          <t>Lappula deflexa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bruch</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Wahlenb.) Garcke</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mt. Juvtábakte (N of Östansjö, NW of Arjeplog), 445 masl (NHWP488), Pi lm</t>
+          <t>Judapakte SO, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613011</v>
+        <v>612966</v>
       </c>
       <c r="R17" t="n">
-        <v>7333581</v>
+        <v>7333559</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2363,12 +2364,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-08-23</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-08-23</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,71 +2383,85 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Rock face on steep S.-facing slope in open birch/conifer woodland</t>
+          <t>under bergbrant</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>Umeå-Herbarium UME</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>17-228</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Mats G Nettelbladt</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Niklas Lönnell, Nick Hodgetts</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Mats G Nettelbladt, Maj-Lis Granström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72337580</t>
+          <t>https://artportalen.se/Sighting/68739041</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110047480</v>
+        <v>72337580</v>
       </c>
       <c r="B18" t="n">
-        <v>93197</v>
+        <v>96445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>2665</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordlig fjädermossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neckera oligocarpa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Bruch</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Akkelis utvidgning-Silvervägen, Pi lm</t>
+          <t>Mt. Juvtábakte (N of Östansjö, NW of Arjeplog), 445 masl (NHWP488), Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>612979</v>
+        <v>613011</v>
       </c>
       <c r="R18" t="n">
-        <v>7333708</v>
+        <v>7333581</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2470,12 +2485,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2017-08-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
+          <t>2017-08-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2486,31 +2501,36 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Rock face on steep S.-facing slope in open birch/conifer woodland</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Niklas Lönnell, Nick Hodgetts</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110047480</t>
+          <t>https://artportalen.se/Sighting/72337580</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110047703</v>
+        <v>110047480</v>
       </c>
       <c r="B19" t="n">
-        <v>91909</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,21 +2538,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614574</v>
+        <v>612979</v>
       </c>
       <c r="R19" t="n">
-        <v>7334375</v>
+        <v>7333708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,12 +2592,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,16 +2623,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110047703</t>
+          <t>https://artportalen.se/Sighting/110047480</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110047700</v>
+        <v>110047703</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,21 +2640,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614449</v>
+        <v>614574</v>
       </c>
       <c r="R20" t="n">
-        <v>7334498</v>
+        <v>7334375</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,13 +2725,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110047700</t>
+          <t>https://artportalen.se/Sighting/110047703</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110047708</v>
+        <v>110047700</v>
       </c>
       <c r="B21" t="n">
         <v>57953</v>
@@ -2746,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614534</v>
+        <v>614449</v>
       </c>
       <c r="R21" t="n">
-        <v>7334351</v>
+        <v>7334498</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,16 +2827,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110047708</t>
+          <t>https://artportalen.se/Sighting/110047700</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110047712</v>
+        <v>110047708</v>
       </c>
       <c r="B22" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,16 +2844,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2848,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614288</v>
+        <v>614534</v>
       </c>
       <c r="R22" t="n">
-        <v>7334665</v>
+        <v>7334351</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2909,16 +2929,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110047712</t>
+          <t>https://artportalen.se/Sighting/110047708</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110047705</v>
+        <v>110047712</v>
       </c>
       <c r="B23" t="n">
-        <v>91909</v>
+        <v>58057</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,21 +2946,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2950,10 +2970,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614619</v>
+        <v>614288</v>
       </c>
       <c r="R23" t="n">
-        <v>7334406</v>
+        <v>7334665</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3010,6 +3030,108 @@
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110047712</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>110047705</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Akkelis utvidgning-Silvervägen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>614619</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7334406</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-08-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-08-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110047705</t>
         </is>
@@ -3039,6 +3161,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
